--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_strength_assignments.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_strength_assignments.xlsx
@@ -431,7 +431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Site</t>
+          <t>StationID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -504,7 +504,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>

--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_strength_assignments.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_strength_assignments.xlsx
@@ -425,15 +425,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>StationID</t>
-        </is>
-      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Env_Silhouette</t>
@@ -463,68 +458,68 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0379</v>
+        <v>0.0143</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2998</v>
+        <v>0.3771</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6786</v>
+        <v>0.6819</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3788</v>
+        <v>-0.3048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.5142</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0382</v>
+        <v>0.5067</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9882</v>
+        <v>0.6236</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.95</v>
+        <v>-0.1169</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.23</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6982</v>
+        <v>0.4827</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9619</v>
+        <v>0.6382</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2637</v>
+        <v>-0.1555</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -535,20 +530,20 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.0799</v>
+        <v>0.026</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6654</v>
+        <v>0.5821</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8929</v>
+        <v>0.3891</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2275</v>
+        <v>0.1931</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -559,20 +554,20 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1098</v>
+        <v>0.1113</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7009</v>
+        <v>0.5939</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2092</v>
+        <v>0.3708</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4917</v>
+        <v>0.2231</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -583,188 +578,188 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2276</v>
+        <v>-0.0994</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7947</v>
+        <v>0.4526</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2132</v>
+        <v>0.6555</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5815</v>
+        <v>-0.2029</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.0919</v>
+        <v>0.037</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1934</v>
+        <v>0.0071</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7284</v>
+        <v>0.002</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.535</v>
+        <v>0.0051</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1909</v>
+        <v>-0.131</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7105</v>
+        <v>0.4211</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2046</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5058</v>
+        <v>-0.1107</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.0438</v>
+        <v>-0.0508</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2039</v>
+        <v>0.6218</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7244</v>
+        <v>0.7179</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5205</v>
+        <v>-0.0961</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.0413</v>
+        <v>-0.0872</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7752</v>
+        <v>0.5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2325</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5427</v>
+        <v>-0.1305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1911</v>
+        <v>-0.0211</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7865</v>
+        <v>0.3748</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2181</v>
+        <v>0.6591</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5684</v>
+        <v>-0.2843</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.0034</v>
+        <v>-0.5422</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0493</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0487</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0122</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.0977</v>
+        <v>0.0593</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4679</v>
+        <v>0.635</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6286</v>
+        <v>0.5722</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1607</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -775,20 +770,20 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1192</v>
+        <v>-0.1286</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6965</v>
+        <v>0.4866</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9593</v>
+        <v>0.6284</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2628</v>
+        <v>-0.1418</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -799,44 +794,44 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1432</v>
+        <v>-0.0711</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7453</v>
+        <v>0.7019</v>
       </c>
       <c r="D16" t="n">
-        <v>0.219</v>
+        <v>0.6515</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5263</v>
+        <v>0.0504</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.0823</v>
+        <v>0.1248</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3032</v>
+        <v>0.5121</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6806</v>
+        <v>0.4673</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3774</v>
+        <v>0.0448</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -847,20 +842,20 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.0136</v>
+        <v>0.0893</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6394</v>
+        <v>0.5115</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3043</v>
+        <v>0.495</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3352</v>
+        <v>0.0164</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -871,20 +866,20 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.0218</v>
+        <v>-0.1463</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8808</v>
+        <v>0.5117</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6709000000000001</v>
+        <v>0.5784</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2099</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -895,20 +890,20 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0053</v>
+        <v>0.0898</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2027</v>
+        <v>0.3944</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7262</v>
+        <v>0.6323</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5236</v>
+        <v>-0.2379</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -919,20 +914,20 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0979</v>
+        <v>-0.0462</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3825</v>
+        <v>0.6242</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5915</v>
+        <v>0.7123</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.209</v>
+        <v>-0.0881</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -943,68 +938,68 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.078</v>
+        <v>0.0701</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7812</v>
+        <v>0.3953</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2322</v>
+        <v>0.6375</v>
       </c>
       <c r="E22" t="n">
-        <v>0.549</v>
+        <v>-0.2422</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0153</v>
+        <v>0.0751</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9843</v>
+        <v>0.3696</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7178</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2665</v>
+        <v>-0.2892</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.0825</v>
+        <v>-0.1444</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7078</v>
+        <v>0.5298</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9848</v>
+        <v>0.5849</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.277</v>
+        <v>-0.0551</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1015,20 +1010,20 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2043</v>
+        <v>0.0325</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.6272</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7117</v>
+        <v>0.7144</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2686</v>
+        <v>-0.0872</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1039,44 +1034,44 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.2428</v>
+        <v>-0.0205</v>
       </c>
       <c r="C26" t="n">
-        <v>0.705</v>
+        <v>0.6269</v>
       </c>
       <c r="D26" t="n">
-        <v>0.983</v>
+        <v>0.713</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2781</v>
+        <v>-0.0861</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0219</v>
+        <v>0.0467</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7083</v>
+        <v>0.6976</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9845</v>
+        <v>0.6485</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2761</v>
+        <v>0.0491</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1087,20 +1082,20 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0658</v>
+        <v>-0.0319</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7034</v>
+        <v>0.6345</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9627</v>
+        <v>0.7186</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2593</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1111,20 +1106,20 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0648</v>
+        <v>0.1276</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5513</v>
+        <v>0.701</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6066</v>
+        <v>0.6518</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0552</v>
+        <v>0.0492</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1135,20 +1130,20 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0047</v>
+        <v>-0.031</v>
       </c>
       <c r="C30" t="n">
-        <v>0.708</v>
+        <v>0.6341</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9846</v>
+        <v>0.7204</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2766</v>
+        <v>-0.0863</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1159,44 +1154,44 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0251</v>
+        <v>-0.0168</v>
       </c>
       <c r="C31" t="n">
-        <v>0.708</v>
+        <v>0.6995</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9813</v>
+        <v>0.6511</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2733</v>
+        <v>0.0484</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.0677</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6965</v>
+        <v>0.7008</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.6536</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2507</v>
+        <v>0.0472</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1207,20 +1202,20 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1376</v>
+        <v>0.0856</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4791</v>
+        <v>0.7016</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4733</v>
+        <v>0.6476</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0058</v>
+        <v>0.054</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1231,20 +1226,20 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.1402</v>
+        <v>0.0847</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9786</v>
+        <v>0.5068</v>
       </c>
       <c r="D34" t="n">
-        <v>0.7129</v>
+        <v>0.449</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2657</v>
+        <v>0.0578</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1255,20 +1250,20 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.14</v>
+        <v>-0.0907</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7064</v>
+        <v>0.4896</v>
       </c>
       <c r="D35" t="n">
-        <v>0.985</v>
+        <v>0.6421</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.2787</v>
+        <v>-0.1525</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1279,20 +1274,20 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.08500000000000001</v>
+        <v>0.1125</v>
       </c>
       <c r="C36" t="n">
-        <v>0.7075</v>
+        <v>0.7008</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9845</v>
+        <v>0.6488</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.277</v>
+        <v>0.052</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1303,20 +1298,20 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.0725</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7088</v>
+        <v>0.4374</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9848</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.2761</v>
+        <v>-0.1126</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1327,68 +1322,68 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.2208</v>
+        <v>0.0344</v>
       </c>
       <c r="C38" t="n">
-        <v>0.707</v>
+        <v>0.6992</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9843</v>
+        <v>0.6495</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.2773</v>
+        <v>0.0497</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.1101</v>
+        <v>-0.0316</v>
       </c>
       <c r="C39" t="n">
-        <v>0.71</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9842</v>
+        <v>0.7145</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.2742</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.0595</v>
+        <v>-0.0139</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7093</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9843</v>
+        <v>0.7121</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.2751</v>
+        <v>-0.0916</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1399,20 +1394,20 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.177</v>
+        <v>0.0033</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9858</v>
+        <v>0.6288</v>
       </c>
       <c r="D41" t="n">
-        <v>0.7179</v>
+        <v>0.7169</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2679</v>
+        <v>-0.0881</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1423,20 +1418,20 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.2816</v>
+        <v>-0.0199</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7062</v>
+        <v>0.4115</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.681</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.2793</v>
+        <v>-0.2694</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1447,216 +1442,24 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>DR-157</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.2006</v>
+        <v>-0.0306</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9826</v>
+        <v>0.6278</v>
       </c>
       <c r="D43" t="n">
-        <v>0.715</v>
+        <v>0.7141</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2676</v>
+        <v>-0.0863</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>Strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>S65</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>-0.0955</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0.7094</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0.9841</v>
-      </c>
-      <c r="E44" t="n">
-        <v>-0.2747</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>S69</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0.9831</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0.7167</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0.2664</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>S70</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>0.1245</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0.9809</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0.7151999999999999</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.2657</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>S72</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>0.1703</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0.7163</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.2672</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>S74</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>0.1133</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0.9709</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.7114</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.2594</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>S79</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>-0.0443</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0.6994</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0.9335</v>
-      </c>
-      <c r="E49" t="n">
-        <v>-0.2341</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>-0.0898</v>
-      </c>
-      <c r="C50" t="n">
-        <v>0.7065</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0.9831</v>
-      </c>
-      <c r="E50" t="n">
-        <v>-0.2765</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>S81</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>-0.0566</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.739</v>
-      </c>
-      <c r="E51" t="n">
-        <v>-0.533</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Weak</t>
         </is>
       </c>
     </row>

--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_strength_assignments.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_strength_assignments.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,40 +462,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0143</v>
+        <v>0.0533</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3771</v>
+        <v>0.767</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6819</v>
+        <v>0.5633</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3048</v>
+        <v>0.2037</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>DR-10</t>
+          <t>DR-94</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.09039999999999999</v>
+        <v>0.0011</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5067</v>
+        <v>0.7891</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6236</v>
+        <v>0.6081</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1169</v>
+        <v>0.181</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -506,44 +506,44 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>DR-54</t>
+          <t>DR-103</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.1175</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4827</v>
+        <v>0.1075</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6382</v>
+        <v>0.438</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1555</v>
+        <v>-0.3305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>DR-163</t>
+          <t>SCR-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.026</v>
+        <v>0.1654</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5821</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3891</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1931</v>
+        <v>0.2086</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -554,20 +554,20 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>DR-164</t>
+          <t>SCR-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1113</v>
+        <v>0.3912</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5939</v>
+        <v>0.6092</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3708</v>
+        <v>0.1602</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2231</v>
+        <v>0.449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -578,44 +578,44 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>DR-167</t>
+          <t>LSC-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0994</v>
+        <v>0.19</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4526</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6555</v>
+        <v>0.6135</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2029</v>
+        <v>0.1924</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>DR-168</t>
+          <t>DR-125</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.037</v>
+        <v>0.2896</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0071</v>
+        <v>0.6097</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002</v>
+        <v>0.1753</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0051</v>
+        <v>0.4343</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -626,116 +626,116 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>DR-175</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.131</v>
+        <v>0.0011</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4211</v>
+        <v>0.0342</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.0954</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1107</v>
+        <v>-0.0612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>DR-195</t>
+          <t>LSC-12</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.0508</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6218</v>
+        <v>0.2273</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7179</v>
+        <v>0.339</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0961</v>
+        <v>-0.1117</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>DR-197</t>
+          <t>SCR-04</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.0872</v>
+        <v>-0.0052</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5</v>
+        <v>0.7438</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.7328</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1305</v>
+        <v>0.011</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>DR-202</t>
+          <t>SCR-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.0211</v>
+        <v>0.2501</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3748</v>
+        <v>0.8089</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6591</v>
+        <v>0.5981</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2843</v>
+        <v>0.2108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-204</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.5422</v>
+        <v>-0.1441</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.1031</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.7383</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0122</v>
+        <v>-0.6352</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -746,68 +746,68 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>DR-205</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0593</v>
+        <v>-0.4039</v>
       </c>
       <c r="C14" t="n">
-        <v>0.635</v>
+        <v>0.0342</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5722</v>
+        <v>0.6692</v>
       </c>
       <c r="E14" t="n">
-        <v>0.06279999999999999</v>
+        <v>-0.635</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>DR-206</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1286</v>
+        <v>-0.0159</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4866</v>
+        <v>0.7901</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6284</v>
+        <v>0.6409</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1418</v>
+        <v>0.1491</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>DR-207</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.0711</v>
+        <v>-0.1076</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7019</v>
+        <v>0.6994</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6515</v>
+        <v>0.7371</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0504</v>
+        <v>-0.0377</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -818,20 +818,20 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>DR-208</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1248</v>
+        <v>0.2777</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5121</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4673</v>
+        <v>0.1628</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0448</v>
+        <v>0.4415</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -842,20 +842,20 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>DR-209</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0893</v>
+        <v>0.1534</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5115</v>
+        <v>0.8001</v>
       </c>
       <c r="D18" t="n">
-        <v>0.495</v>
+        <v>0.6466</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0164</v>
+        <v>0.1534</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -866,20 +866,20 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>DR-15</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.1463</v>
+        <v>0.3124</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5117</v>
+        <v>0.6056</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5784</v>
+        <v>0.1604</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.06660000000000001</v>
+        <v>0.4452</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -890,44 +890,44 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>DR-17</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0898</v>
+        <v>0.1401</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3944</v>
+        <v>0.8038</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6323</v>
+        <v>0.626</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2379</v>
+        <v>0.1778</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>DR-18</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.0462</v>
+        <v>0.0391</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6242</v>
+        <v>0.7163</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7123</v>
+        <v>0.7359</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0881</v>
+        <v>-0.0197</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -938,20 +938,20 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>DR-19</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0701</v>
+        <v>-0.1993</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3953</v>
+        <v>0.2439</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6375</v>
+        <v>0.379</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2422</v>
+        <v>-0.135</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -962,44 +962,44 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>DR-20</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0751</v>
+        <v>0.2256</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3696</v>
+        <v>0.8017</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2892</v>
+        <v>0.2165</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>DR-23</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1444</v>
+        <v>0.2116</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5298</v>
+        <v>0.8038</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5849</v>
+        <v>0.5898</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0551</v>
+        <v>0.214</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1010,20 +1010,20 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>DR-38</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0325</v>
+        <v>0.098</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6272</v>
+        <v>0.78</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7144</v>
+        <v>0.5702</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0872</v>
+        <v>0.2098</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1034,20 +1034,20 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>DR-40</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0205</v>
+        <v>0.226</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6269</v>
+        <v>0.8101</v>
       </c>
       <c r="D26" t="n">
-        <v>0.713</v>
+        <v>0.6031</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0861</v>
+        <v>0.207</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1058,20 +1058,20 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>DR-44</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0467</v>
+        <v>0.1858</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6976</v>
+        <v>0.7867</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6485</v>
+        <v>0.5759</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0491</v>
+        <v>0.2109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1082,20 +1082,20 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>DR-45</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0319</v>
+        <v>0.0258</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6345</v>
+        <v>0.2457</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7186</v>
+        <v>0.251</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.0053</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1106,20 +1106,20 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>DR-48</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1276</v>
+        <v>0.2119</v>
       </c>
       <c r="C29" t="n">
-        <v>0.701</v>
+        <v>0.8062</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6518</v>
+        <v>0.5926</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0492</v>
+        <v>0.2136</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1130,20 +1130,20 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>DR-49</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.031</v>
+        <v>0.2374</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6341</v>
+        <v>0.8038</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7204</v>
+        <v>0.5894</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0863</v>
+        <v>0.2144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1154,44 +1154,44 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>DR-50</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0168</v>
+        <v>0.2107</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6995</v>
+        <v>0.8058</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6511</v>
+        <v>0.5946</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0484</v>
+        <v>0.2112</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>DR-51</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0677</v>
+        <v>0.03</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7008</v>
+        <v>0.7996</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6536</v>
+        <v>0.6478</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0472</v>
+        <v>0.1519</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1202,20 +1202,20 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>DR-53</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0856</v>
+        <v>0.0674</v>
       </c>
       <c r="C33" t="n">
-        <v>0.7016</v>
+        <v>0.7679</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6476</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>0.054</v>
+        <v>0.0789</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1226,20 +1226,20 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>DR-55</t>
+          <t>LSC-30</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0847</v>
+        <v>0.0936</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5068</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>0.449</v>
+        <v>0.6142</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0578</v>
+        <v>0.1928</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1250,20 +1250,20 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>DR-56</t>
+          <t>LSC-32</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.0907</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4896</v>
+        <v>0.6879</v>
       </c>
       <c r="D35" t="n">
-        <v>0.6421</v>
+        <v>0.7331</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.1525</v>
+        <v>-0.0451</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1274,44 +1274,44 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>DR-59</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.1125</v>
+        <v>-0.1654</v>
       </c>
       <c r="C36" t="n">
-        <v>0.7008</v>
+        <v>0.6847</v>
       </c>
       <c r="D36" t="n">
-        <v>0.6488</v>
+        <v>0.7333</v>
       </c>
       <c r="E36" t="n">
-        <v>0.052</v>
+        <v>-0.0485</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-09</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.09710000000000001</v>
+        <v>0.1776</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4374</v>
+        <v>0.8062</v>
       </c>
       <c r="D37" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.5991</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.1126</v>
+        <v>0.2071</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1322,20 +1322,20 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>DR-140</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.0344</v>
+        <v>0.2091</v>
       </c>
       <c r="C38" t="n">
-        <v>0.6992</v>
+        <v>0.8092</v>
       </c>
       <c r="D38" t="n">
-        <v>0.6495</v>
+        <v>0.6005</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0497</v>
+        <v>0.2086</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1346,20 +1346,20 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.0316</v>
+        <v>-0.0188</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.7022</v>
       </c>
       <c r="D39" t="n">
-        <v>0.7145</v>
+        <v>0.7398</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.0376</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1370,20 +1370,20 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.0139</v>
+        <v>0.0353</v>
       </c>
       <c r="C40" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.7902</v>
       </c>
       <c r="D40" t="n">
-        <v>0.7121</v>
+        <v>0.6229</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.0916</v>
+        <v>0.1674</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1394,20 +1394,20 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.0033</v>
+        <v>0.0934</v>
       </c>
       <c r="C41" t="n">
-        <v>0.6288</v>
+        <v>0.6997</v>
       </c>
       <c r="D41" t="n">
-        <v>0.7169</v>
+        <v>0.7373</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.0881</v>
+        <v>-0.0376</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1418,48 +1418,456 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>DR-144</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.0199</v>
+        <v>0.0599</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4115</v>
+        <v>0.7032</v>
       </c>
       <c r="D42" t="n">
-        <v>0.681</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.2694</v>
+        <v>0.0011</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
+          <t>LSC-45</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>-0.0609</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7074</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.7368</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-0.0294</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>LSC-47</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.6981000000000001</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>LSC-48</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.0917</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.7003</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-0.0056</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>LSC-53</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.1853</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.8089</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.5997</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.2092</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>LSC-55</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.7177</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.7398</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-0.0221</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>LSC-56</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>-0.0857</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.7736</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.6797</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.0939</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>LSC-57</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0.1307</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.8083</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.5999</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.2084</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>LSC-58</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.7489</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.7247</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>LSC-59</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>-0.1965</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.8022</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-0.2342</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>LSC-60</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>-0.1725</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.7418</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-0.0378</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.7328</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.7345</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.1779</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.6037</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.2063</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>-0.3644</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.1185</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.6716</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-0.5531</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.2144</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.8062</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.5933</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.2129</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>-0.0648</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.7183</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.7443</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.1886</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.8105</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.6015</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
           <t>DR-157</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>-0.0306</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0.6278</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.7141</v>
-      </c>
-      <c r="E43" t="n">
-        <v>-0.0863</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Strong</t>
+      <c r="B59" t="n">
+        <v>0.1955</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.8071</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.2102</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>DR-159</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>-0.2264</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.1232</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.6682</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-0.545</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Weak</t>
         </is>
       </c>
     </row>

--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_strength_assignments.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_strength_assignments.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,20 +462,20 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0533</v>
+        <v>-0.0376</v>
       </c>
       <c r="C2" t="n">
-        <v>0.767</v>
+        <v>0.7792</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5633</v>
+        <v>0.5931</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2037</v>
+        <v>0.1861</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -486,20 +486,20 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0011</v>
+        <v>-0.049</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7891</v>
+        <v>0.7749</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6081</v>
+        <v>0.638</v>
       </c>
       <c r="E3" t="n">
-        <v>0.181</v>
+        <v>0.1369</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.1175</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1075</v>
+        <v>0.5235</v>
       </c>
       <c r="D4" t="n">
-        <v>0.438</v>
+        <v>0.3944</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3305</v>
+        <v>0.1291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -534,16 +534,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1654</v>
+        <v>0.1272</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.806</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.615</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2086</v>
+        <v>0.1911</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3912</v>
+        <v>0.4366</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6092</v>
+        <v>0.7687</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1602</v>
+        <v>0.1502</v>
       </c>
       <c r="E6" t="n">
-        <v>0.449</v>
+        <v>0.6185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -582,20 +582,20 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.19</v>
+        <v>-0.1605</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.6128</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6135</v>
+        <v>0.8043</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1924</v>
+        <v>-0.1915</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2896</v>
+        <v>0.3467</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6097</v>
+        <v>0.7574</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1753</v>
+        <v>0.1716</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4343</v>
+        <v>0.5858</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -630,20 +630,20 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0011</v>
+        <v>-0.0251</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0342</v>
+        <v>0.0106</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0954</v>
+        <v>0.1059</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0612</v>
+        <v>-0.0953</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -654,20 +654,20 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.09810000000000001</v>
+        <v>0.1197</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2273</v>
+        <v>0.4219</v>
       </c>
       <c r="D10" t="n">
-        <v>0.339</v>
+        <v>0.2997</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1117</v>
+        <v>0.1222</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
@@ -678,20 +678,20 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.0052</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7438</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7328</v>
+        <v>0.7126</v>
       </c>
       <c r="E11" t="n">
-        <v>0.011</v>
+        <v>0.0288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -702,16 +702,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2501</v>
+        <v>0.2045</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8089</v>
+        <v>0.8082</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5981</v>
+        <v>0.6159</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2108</v>
+        <v>0.1922</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -722,20 +722,20 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-141</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.1441</v>
+        <v>-0.4468</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1031</v>
+        <v>0.0659</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7383</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6352</v>
+        <v>-0.7391</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -746,116 +746,116 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>DR-143</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.4039</v>
+        <v>0.0008</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0342</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6692</v>
+        <v>0.6387</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.635</v>
+        <v>0.1329</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SCR-11</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.0159</v>
+        <v>-0.0673</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7901</v>
+        <v>0.7343</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6409</v>
+        <v>0.7146</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1491</v>
+        <v>0.0198</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SCR-14</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1076</v>
+        <v>0.41</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6994</v>
+        <v>0.758</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7371</v>
+        <v>0.1673</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0377</v>
+        <v>0.5907</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>SCR-17</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2777</v>
+        <v>0.0814</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.7794</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1628</v>
+        <v>0.6866</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4415</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>SCR-18</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1534</v>
+        <v>0.4027</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8001</v>
+        <v>0.7563</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6466</v>
+        <v>0.1624</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1534</v>
+        <v>0.5939</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -866,20 +866,20 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>SCR-19</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3124</v>
+        <v>0.0313</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6056</v>
+        <v>0.7963</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1604</v>
+        <v>0.6586</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4452</v>
+        <v>0.1377</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -890,92 +890,92 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>SCR-20</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1401</v>
+        <v>-0.0694</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8038</v>
+        <v>0.7362</v>
       </c>
       <c r="D20" t="n">
-        <v>0.626</v>
+        <v>0.7084</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1778</v>
+        <v>0.0278</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>LSC-14</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0391</v>
+        <v>-0.1462</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7163</v>
+        <v>0.3627</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7359</v>
+        <v>0.5593</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0197</v>
+        <v>-0.1966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>LSC-15</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1993</v>
+        <v>0.172</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2439</v>
+        <v>0.8099</v>
       </c>
       <c r="D22" t="n">
-        <v>0.379</v>
+        <v>0.6214</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.135</v>
+        <v>0.1885</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>LSC-16</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2256</v>
+        <v>0.1741</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8017</v>
+        <v>0.8084</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.6196</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2165</v>
+        <v>0.1888</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -986,20 +986,20 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2116</v>
+        <v>0.1075</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8038</v>
+        <v>0.7984</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5898</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>0.214</v>
+        <v>0.2011</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1010,20 +1010,20 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>LSC-18</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.098</v>
+        <v>0.2139</v>
       </c>
       <c r="C25" t="n">
-        <v>0.78</v>
+        <v>0.8064</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5702</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2098</v>
+        <v>0.192</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1034,20 +1034,20 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>LSC-19</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.226</v>
+        <v>0.2019</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8101</v>
+        <v>0.7996</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6031</v>
+        <v>0.5999</v>
       </c>
       <c r="E26" t="n">
-        <v>0.207</v>
+        <v>0.1997</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1058,20 +1058,20 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>LSC-22</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1858</v>
+        <v>0.0655</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7867</v>
+        <v>0.4168</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5759</v>
+        <v>0.2887</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2109</v>
+        <v>0.128</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1082,20 +1082,20 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>LSC-23</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0258</v>
+        <v>0.121</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2457</v>
+        <v>0.8024</v>
       </c>
       <c r="D28" t="n">
-        <v>0.251</v>
+        <v>0.6039</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0053</v>
+        <v>0.1985</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1106,20 +1106,20 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2119</v>
+        <v>0.1603</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8062</v>
+        <v>0.8045</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5926</v>
+        <v>0.6101</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2136</v>
+        <v>0.1944</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1130,20 +1130,20 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>LSC-25</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2374</v>
+        <v>0.1507</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8038</v>
+        <v>0.8074</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5894</v>
+        <v>0.6171</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2144</v>
+        <v>0.1903</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1154,20 +1154,20 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>LSC-26</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.2107</v>
+        <v>0.0027</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8058</v>
+        <v>0.7864</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5946</v>
+        <v>0.6472</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2112</v>
+        <v>0.1393</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1178,68 +1178,68 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>LSC-27</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.03</v>
+        <v>-0.1896</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7996</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6478</v>
+        <v>0.7713</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1519</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>SCR-06</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0674</v>
+        <v>-0.0688</v>
       </c>
       <c r="C33" t="n">
-        <v>0.7679</v>
+        <v>0.681</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.7109</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0789</v>
+        <v>-0.0299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>LSC-30</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0936</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8097</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6142</v>
+        <v>0.6211</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1928</v>
+        <v>0.1886</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1250,44 +1250,44 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>LSC-32</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.07439999999999999</v>
+        <v>0.1516</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6879</v>
+        <v>0.8055</v>
       </c>
       <c r="D35" t="n">
-        <v>0.7331</v>
+        <v>0.6152</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.0451</v>
+        <v>0.1903</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>LSC-37</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.1654</v>
+        <v>0.0286</v>
       </c>
       <c r="C36" t="n">
-        <v>0.6847</v>
+        <v>0.696</v>
       </c>
       <c r="D36" t="n">
-        <v>0.7333</v>
+        <v>0.7352</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.0485</v>
+        <v>-0.0393</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1298,116 +1298,116 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-38</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.1776</v>
+        <v>-0.0532</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8062</v>
+        <v>0.7825</v>
       </c>
       <c r="D37" t="n">
-        <v>0.5991</v>
+        <v>0.6337</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2071</v>
+        <v>0.1489</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>LSC-39</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.2091</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8092</v>
+        <v>0.6944</v>
       </c>
       <c r="D38" t="n">
-        <v>0.6005</v>
+        <v>0.7202</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2086</v>
+        <v>-0.0258</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-40</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.0188</v>
+        <v>0.0492</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7022</v>
+        <v>0.6945</v>
       </c>
       <c r="D39" t="n">
-        <v>0.7398</v>
+        <v>0.7274</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.0376</v>
+        <v>-0.0329</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-41</t>
+          <t>LSC-45</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.0353</v>
+        <v>0.0239</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7902</v>
+        <v>0.7377</v>
       </c>
       <c r="D40" t="n">
-        <v>0.6229</v>
+        <v>0.7121</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1674</v>
+        <v>0.0256</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-42</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.0934</v>
+        <v>0.135</v>
       </c>
       <c r="C41" t="n">
-        <v>0.6997</v>
+        <v>0.8065</v>
       </c>
       <c r="D41" t="n">
-        <v>0.7373</v>
+        <v>0.6165</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.0376</v>
+        <v>0.1901</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1418,188 +1418,188 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>LSC-43</t>
+          <t>LSC-55</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.0599</v>
+        <v>0.0219</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7032</v>
+        <v>0.7308</v>
       </c>
       <c r="D42" t="n">
-        <v>0.7020999999999999</v>
+        <v>0.7178</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0011</v>
+        <v>0.013</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>LSC-45</t>
+          <t>LSC-56</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.0609</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7074</v>
+        <v>0.7325</v>
       </c>
       <c r="D43" t="n">
-        <v>0.7368</v>
+        <v>0.721</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.0294</v>
+        <v>0.0115</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>LSC-47</t>
+          <t>LSC-57</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.08790000000000001</v>
+        <v>-0.0785</v>
       </c>
       <c r="C44" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.5856</v>
       </c>
       <c r="D44" t="n">
-        <v>0.697</v>
+        <v>0.8125</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0012</v>
+        <v>-0.2269</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>LSC-48</t>
+          <t>LSC-58</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.0917</v>
+        <v>-0.0476</v>
       </c>
       <c r="C45" t="n">
-        <v>0.7003</v>
+        <v>0.6791</v>
       </c>
       <c r="D45" t="n">
-        <v>0.706</v>
+        <v>0.7534</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.0056</v>
+        <v>-0.0743</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-59</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.1853</v>
+        <v>-0.0626</v>
       </c>
       <c r="C46" t="n">
-        <v>0.8089</v>
+        <v>0.6485</v>
       </c>
       <c r="D46" t="n">
-        <v>0.5997</v>
+        <v>0.7967</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2092</v>
+        <v>-0.1482</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>LSC-55</t>
+          <t>LSC-60</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0145</v>
+        <v>0.0292</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7177</v>
+        <v>0.6974</v>
       </c>
       <c r="D47" t="n">
-        <v>0.7398</v>
+        <v>0.7268</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.0221</v>
+        <v>-0.0294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>LSC-56</t>
+          <t>LSC-62</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.0857</v>
+        <v>0.0028</v>
       </c>
       <c r="C48" t="n">
-        <v>0.7736</v>
+        <v>0.7227</v>
       </c>
       <c r="D48" t="n">
-        <v>0.6797</v>
+        <v>0.7169</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0939</v>
+        <v>0.0057</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>LSC-57</t>
+          <t>SCR-08</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.1307</v>
+        <v>0.1292</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8083</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>0.5999</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2084</v>
+        <v>0.1895</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1610,44 +1610,44 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>LSC-58</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.045</v>
+        <v>-0.4042</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7489</v>
+        <v>0.1357</v>
       </c>
       <c r="D50" t="n">
-        <v>0.7247</v>
+        <v>0.8076</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0242</v>
+        <v>-0.672</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>LSC-59</t>
+          <t>DR-145</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.1965</v>
+        <v>0.1937</v>
       </c>
       <c r="C51" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.8078</v>
       </c>
       <c r="D51" t="n">
-        <v>0.8022</v>
+        <v>0.6182</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.2342</v>
+        <v>0.1896</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -1658,20 +1658,20 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>LSC-60</t>
+          <t>SCR-09</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.1725</v>
+        <v>-0.0544</v>
       </c>
       <c r="C52" t="n">
-        <v>0.704</v>
+        <v>0.7339</v>
       </c>
       <c r="D52" t="n">
-        <v>0.7418</v>
+        <v>0.7158</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.0378</v>
+        <v>0.0181</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -1682,190 +1682,22 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>LSC-62</t>
+          <t>DR-159</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.0002</v>
+        <v>-0.3025</v>
       </c>
       <c r="C53" t="n">
-        <v>0.7328</v>
+        <v>0.157</v>
       </c>
       <c r="D53" t="n">
-        <v>0.7345</v>
+        <v>0.8044</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0016</v>
+        <v>-0.6475</v>
       </c>
       <c r="F53" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>SCR-08</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>0.1779</v>
-      </c>
-      <c r="C54" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.6037</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.2063</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>DR-144</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>-0.3644</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0.1185</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0.6716</v>
-      </c>
-      <c r="E55" t="n">
-        <v>-0.5531</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>DR-145</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>0.2144</v>
-      </c>
-      <c r="C56" t="n">
-        <v>0.8062</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0.5933</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0.2129</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>SCR-09</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>-0.0648</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0.7183</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0.7443</v>
-      </c>
-      <c r="E57" t="n">
-        <v>-0.026</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>DR-156</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>0.1886</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0.8105</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0.6015</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>DR-157</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>0.1955</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0.8071</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0.597</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0.2102</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>DR-159</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>-0.2264</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0.1232</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0.6682</v>
-      </c>
-      <c r="E60" t="n">
-        <v>-0.545</v>
-      </c>
-      <c r="F60" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>

--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_strength_assignments.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_strength_assignments.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,20 +462,20 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.0376</v>
+        <v>0.0533</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7792</v>
+        <v>0.767</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5931</v>
+        <v>0.5633</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1861</v>
+        <v>0.2037</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
@@ -486,20 +486,20 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.049</v>
+        <v>0.0011</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7749</v>
+        <v>0.7891</v>
       </c>
       <c r="D3" t="n">
-        <v>0.638</v>
+        <v>0.6081</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1369</v>
+        <v>0.181</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
@@ -510,20 +510,20 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.1175</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5235</v>
+        <v>0.1075</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3944</v>
+        <v>0.438</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1291</v>
+        <v>-0.3305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -534,16 +534,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1272</v>
+        <v>0.1654</v>
       </c>
       <c r="C5" t="n">
-        <v>0.806</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.615</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1911</v>
+        <v>0.2086</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4366</v>
+        <v>0.3912</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7687</v>
+        <v>0.6092</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1502</v>
+        <v>0.1602</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6185</v>
+        <v>0.449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -582,20 +582,20 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.1605</v>
+        <v>0.19</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6128</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8043</v>
+        <v>0.6135</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1915</v>
+        <v>0.1924</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3467</v>
+        <v>0.2896</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7574</v>
+        <v>0.6097</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1716</v>
+        <v>0.1753</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5858</v>
+        <v>0.4343</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -630,20 +630,20 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.0251</v>
+        <v>0.0011</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0106</v>
+        <v>0.0342</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1059</v>
+        <v>0.0954</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0953</v>
+        <v>-0.0612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
@@ -654,20 +654,20 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1197</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4219</v>
+        <v>0.2273</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2997</v>
+        <v>0.339</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1222</v>
+        <v>-0.1117</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -678,16 +678,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0052</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7413999999999999</v>
+        <v>0.7438</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7126</v>
+        <v>0.7328</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0288</v>
+        <v>0.011</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -702,16 +702,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2045</v>
+        <v>0.2501</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8082</v>
+        <v>0.8089</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6159</v>
+        <v>0.5981</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1922</v>
+        <v>0.2108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -722,20 +722,20 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-143</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.4468</v>
+        <v>-0.1441</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0659</v>
+        <v>0.1031</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8048999999999999</v>
+        <v>0.7383</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.7391</v>
+        <v>-0.6352</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -746,44 +746,44 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>SCR-11</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0008</v>
+        <v>-0.4039</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.0342</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6387</v>
+        <v>0.6692</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1329</v>
+        <v>-0.635</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SCR-14</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.0673</v>
+        <v>-0.0159</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7343</v>
+        <v>0.7901</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7146</v>
+        <v>0.6409</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0198</v>
+        <v>0.1491</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -794,68 +794,68 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SCR-17</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.41</v>
+        <v>-0.1076</v>
       </c>
       <c r="C16" t="n">
-        <v>0.758</v>
+        <v>0.6994</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1673</v>
+        <v>0.7371</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5907</v>
+        <v>-0.0377</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>SCR-18</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.0814</v>
+        <v>0.2777</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7794</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6866</v>
+        <v>0.1628</v>
       </c>
       <c r="E17" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.4415</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>SCR-19</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4027</v>
+        <v>0.1534</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7563</v>
+        <v>0.8001</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1624</v>
+        <v>0.6466</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5939</v>
+        <v>0.1534</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -866,20 +866,20 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>SCR-20</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0313</v>
+        <v>0.3124</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7963</v>
+        <v>0.6056</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6586</v>
+        <v>0.1604</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1377</v>
+        <v>0.4452</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -890,92 +890,92 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>LSC-14</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.0694</v>
+        <v>0.1401</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7362</v>
+        <v>0.8038</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7084</v>
+        <v>0.626</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0278</v>
+        <v>0.1778</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>LSC-15</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.1462</v>
+        <v>0.0391</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3627</v>
+        <v>0.7163</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5593</v>
+        <v>0.7359</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1966</v>
+        <v>-0.0197</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>LSC-16</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.172</v>
+        <v>-0.1993</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8099</v>
+        <v>0.2439</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6214</v>
+        <v>0.379</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1885</v>
+        <v>-0.135</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1741</v>
+        <v>0.2256</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8084</v>
+        <v>0.8017</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6196</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1888</v>
+        <v>0.2165</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -986,20 +986,20 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>LSC-18</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1075</v>
+        <v>0.2116</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7984</v>
+        <v>0.8038</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.5898</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2011</v>
+        <v>0.214</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1010,20 +1010,20 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>LSC-19</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2139</v>
+        <v>0.098</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8064</v>
+        <v>0.78</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6143999999999999</v>
+        <v>0.5702</v>
       </c>
       <c r="E25" t="n">
-        <v>0.192</v>
+        <v>0.2098</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1034,20 +1034,20 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>LSC-22</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2019</v>
+        <v>0.226</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7996</v>
+        <v>0.8101</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5999</v>
+        <v>0.6031</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1997</v>
+        <v>0.207</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1058,20 +1058,20 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>LSC-23</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0655</v>
+        <v>0.1858</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4168</v>
+        <v>0.7867</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2887</v>
+        <v>0.5759</v>
       </c>
       <c r="E27" t="n">
-        <v>0.128</v>
+        <v>0.2109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1082,20 +1082,20 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.121</v>
+        <v>0.0258</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8024</v>
+        <v>0.2457</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6039</v>
+        <v>0.251</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1985</v>
+        <v>-0.0053</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1106,20 +1106,20 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>LSC-25</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1603</v>
+        <v>0.2119</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8045</v>
+        <v>0.8062</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6101</v>
+        <v>0.5926</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1944</v>
+        <v>0.2136</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1130,20 +1130,20 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>LSC-26</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1507</v>
+        <v>0.2374</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8074</v>
+        <v>0.8038</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6171</v>
+        <v>0.5894</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1903</v>
+        <v>0.2144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1154,20 +1154,20 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>LSC-27</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0027</v>
+        <v>0.2107</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7864</v>
+        <v>0.8058</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6472</v>
+        <v>0.5946</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1393</v>
+        <v>0.2112</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1178,68 +1178,68 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>SCR-06</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1896</v>
+        <v>0.03</v>
       </c>
       <c r="C32" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.7996</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7713</v>
+        <v>0.6478</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6929999999999999</v>
+        <v>0.1519</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>LSC-37</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.0688</v>
+        <v>0.0674</v>
       </c>
       <c r="C33" t="n">
-        <v>0.681</v>
+        <v>0.7679</v>
       </c>
       <c r="D33" t="n">
-        <v>0.7109</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.0299</v>
+        <v>0.0789</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>LSC-38</t>
+          <t>LSC-30</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.0936</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8097</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6211</v>
+        <v>0.6142</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1886</v>
+        <v>0.1928</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1250,44 +1250,44 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>LSC-39</t>
+          <t>LSC-32</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.1516</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8055</v>
+        <v>0.6879</v>
       </c>
       <c r="D35" t="n">
-        <v>0.6152</v>
+        <v>0.7331</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1903</v>
+        <v>-0.0451</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>LSC-40</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.0286</v>
+        <v>-0.1654</v>
       </c>
       <c r="C36" t="n">
-        <v>0.696</v>
+        <v>0.6847</v>
       </c>
       <c r="D36" t="n">
-        <v>0.7352</v>
+        <v>0.7333</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.0393</v>
+        <v>-0.0485</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1298,68 +1298,68 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-41</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.0532</v>
+        <v>0.1776</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7825</v>
+        <v>0.8062</v>
       </c>
       <c r="D37" t="n">
-        <v>0.6337</v>
+        <v>0.5991</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1489</v>
+        <v>0.2071</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>LSC-42</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.2091</v>
       </c>
       <c r="C38" t="n">
-        <v>0.6944</v>
+        <v>0.8092</v>
       </c>
       <c r="D38" t="n">
-        <v>0.7202</v>
+        <v>0.6005</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.0258</v>
+        <v>0.2086</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-43</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.0492</v>
+        <v>-0.0188</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6945</v>
+        <v>0.7022</v>
       </c>
       <c r="D39" t="n">
-        <v>0.7274</v>
+        <v>0.7398</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.0329</v>
+        <v>-0.0376</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1370,44 +1370,44 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-45</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.0239</v>
+        <v>0.0353</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7377</v>
+        <v>0.7902</v>
       </c>
       <c r="D40" t="n">
-        <v>0.7121</v>
+        <v>0.6229</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0256</v>
+        <v>0.1674</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.135</v>
+        <v>0.0934</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8065</v>
+        <v>0.6997</v>
       </c>
       <c r="D41" t="n">
-        <v>0.6165</v>
+        <v>0.7373</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1901</v>
+        <v>-0.0376</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1418,44 +1418,44 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>LSC-55</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.0219</v>
+        <v>0.0599</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7308</v>
+        <v>0.7032</v>
       </c>
       <c r="D42" t="n">
-        <v>0.7178</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>0.013</v>
+        <v>0.0011</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>LSC-56</t>
+          <t>LSC-45</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.0609</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7325</v>
+        <v>0.7074</v>
       </c>
       <c r="D43" t="n">
-        <v>0.721</v>
+        <v>0.7368</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0115</v>
+        <v>-0.0294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1466,116 +1466,116 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>LSC-57</t>
+          <t>LSC-47</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.0785</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5856</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>0.8125</v>
+        <v>0.697</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.2269</v>
+        <v>0.0012</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>LSC-58</t>
+          <t>LSC-48</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.0476</v>
+        <v>0.0917</v>
       </c>
       <c r="C45" t="n">
-        <v>0.6791</v>
+        <v>0.7003</v>
       </c>
       <c r="D45" t="n">
-        <v>0.7534</v>
+        <v>0.706</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.0743</v>
+        <v>-0.0056</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>LSC-59</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.0626</v>
+        <v>0.1853</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6485</v>
+        <v>0.8089</v>
       </c>
       <c r="D46" t="n">
-        <v>0.7967</v>
+        <v>0.5997</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.1482</v>
+        <v>0.2092</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>LSC-60</t>
+          <t>LSC-55</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0292</v>
+        <v>0.0145</v>
       </c>
       <c r="C47" t="n">
-        <v>0.6974</v>
+        <v>0.7177</v>
       </c>
       <c r="D47" t="n">
-        <v>0.7268</v>
+        <v>0.7398</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.0294</v>
+        <v>-0.0221</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>LSC-62</t>
+          <t>LSC-56</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.0028</v>
+        <v>-0.0857</v>
       </c>
       <c r="C48" t="n">
-        <v>0.7227</v>
+        <v>0.7736</v>
       </c>
       <c r="D48" t="n">
-        <v>0.7169</v>
+        <v>0.6797</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0057</v>
+        <v>0.0939</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1586,20 +1586,20 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>SCR-08</t>
+          <t>LSC-57</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.1292</v>
+        <v>0.1307</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8083</v>
       </c>
       <c r="D49" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.5999</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1895</v>
+        <v>0.2084</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1610,68 +1610,68 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>DR-144</t>
+          <t>LSC-58</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.4042</v>
+        <v>0.045</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1357</v>
+        <v>0.7489</v>
       </c>
       <c r="D50" t="n">
-        <v>0.8076</v>
+        <v>0.7247</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.672</v>
+        <v>0.0242</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>DR-145</t>
+          <t>LSC-59</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.1937</v>
+        <v>-0.1965</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8078</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>0.6182</v>
+        <v>0.8022</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1896</v>
+        <v>-0.2342</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>SCR-09</t>
+          <t>LSC-60</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.0544</v>
+        <v>-0.1725</v>
       </c>
       <c r="C52" t="n">
-        <v>0.7339</v>
+        <v>0.704</v>
       </c>
       <c r="D52" t="n">
-        <v>0.7158</v>
+        <v>0.7418</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0181</v>
+        <v>-0.0378</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -1682,22 +1682,190 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.7328</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.7345</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.1779</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.6037</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.2063</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>-0.3644</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.1185</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.6716</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-0.5531</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.2144</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.8062</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.5933</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.2129</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>-0.0648</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.7183</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.7443</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.1886</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.8105</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.6015</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>DR-157</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0.1955</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.8071</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.2102</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
           <t>DR-159</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>-0.3025</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0.8044</v>
-      </c>
-      <c r="E53" t="n">
-        <v>-0.6475</v>
-      </c>
-      <c r="F53" t="inlineStr">
+      <c r="B60" t="n">
+        <v>-0.2264</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.1232</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.6682</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-0.545</v>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
